--- a/Data/National Accounts/PSA-08AFF_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-08AFF_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F391A4AE-EEE6-4993-9AB3-A20947741BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC0E305-9BE3-4C8C-9F70-A0FC349625D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AFF" sheetId="1" r:id="rId1"/>
@@ -658,9 +658,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -668,6 +665,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23609,7 +23609,7 @@
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -23620,7 +23620,7 @@
     </row>
     <row r="6" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -23823,10 +23823,10 @@
         <v>415364.39652491623</v>
       </c>
       <c r="Z12" s="8">
-        <v>454878.79744454299</v>
+        <v>454425.27626638132</v>
       </c>
       <c r="AA12" s="8">
-        <v>361557.87915305112</v>
+        <v>360977.02223390184</v>
       </c>
     </row>
     <row r="13" spans="1:27" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -23906,10 +23906,10 @@
         <v>142219.0313550953</v>
       </c>
       <c r="Z13" s="8">
-        <v>116294.06744695638</v>
+        <v>116294.06841549193</v>
       </c>
       <c r="AA13" s="8">
-        <v>116152.15496934913</v>
+        <v>116019.06353752658</v>
       </c>
     </row>
     <row r="14" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -24072,7 +24072,7 @@
         <v>41754.016963909395</v>
       </c>
       <c r="Z15" s="8">
-        <v>34726.55828768119</v>
+        <v>34759.797431076906</v>
       </c>
       <c r="AA15" s="8">
         <v>39379.77012282268</v>
@@ -24155,10 +24155,10 @@
         <v>150479.67286387566</v>
       </c>
       <c r="Z16" s="8">
-        <v>159475.39370606886</v>
+        <v>161464.68735745369</v>
       </c>
       <c r="AA16" s="8">
-        <v>134538.53285356949</v>
+        <v>134530.02246994246</v>
       </c>
     </row>
     <row r="17" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -24238,7 +24238,7 @@
         <v>44251.694293530571</v>
       </c>
       <c r="Z17" s="8">
-        <v>36329.600999374976</v>
+        <v>36376.747266429549</v>
       </c>
       <c r="AA17" s="8">
         <v>43790.865322340855</v>
@@ -24404,7 +24404,7 @@
         <v>7358.1904448176947</v>
       </c>
       <c r="Z19" s="8">
-        <v>11808.755582254305</v>
+        <v>11649.576379175945</v>
       </c>
       <c r="AA19" s="8">
         <v>21245.142162210734</v>
@@ -24487,10 +24487,10 @@
         <v>28711.552520942743</v>
       </c>
       <c r="Z20" s="8">
-        <v>33741.187156617903</v>
+        <v>34354.499194608819</v>
       </c>
       <c r="AA20" s="8">
-        <v>31849.289422777598</v>
+        <v>32335.780394941081</v>
       </c>
     </row>
     <row r="21" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -24573,7 +24573,7 @@
         <v>12511.107066168199</v>
       </c>
       <c r="AA21" s="8">
-        <v>14449.991242380858</v>
+        <v>14448.942947249241</v>
       </c>
     </row>
     <row r="22" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -24653,7 +24653,7 @@
         <v>2134.0651212743724</v>
       </c>
       <c r="Z22" s="8">
-        <v>3267.9079106541531</v>
+        <v>3254.7635842149284</v>
       </c>
       <c r="AA22" s="8">
         <v>5242.7182286930711</v>
@@ -24736,7 +24736,7 @@
         <v>1542.0836068104472</v>
       </c>
       <c r="Z23" s="8">
-        <v>1633.6467866751598</v>
+        <v>1633.728175201185</v>
       </c>
       <c r="AA23" s="8">
         <v>1464.420253510862</v>
@@ -24819,10 +24819,10 @@
         <v>2709.1127588553386</v>
       </c>
       <c r="Z24" s="8">
-        <v>2183.3441974187458</v>
+        <v>2194.863452865623</v>
       </c>
       <c r="AA24" s="8">
-        <v>1918.4700160708794</v>
+        <v>1928.2492653531403</v>
       </c>
     </row>
     <row r="25" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -24902,10 +24902,10 @@
         <v>121587.28017552564</v>
       </c>
       <c r="Z25" s="8">
-        <v>128625.95235675665</v>
+        <v>128469.8579640808</v>
       </c>
       <c r="AA25" s="8">
-        <v>132999.84730796044</v>
+        <v>132617.29289168474</v>
       </c>
     </row>
     <row r="26" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -24985,10 +24985,10 @@
         <v>304869.48535717546</v>
       </c>
       <c r="Z26" s="8">
-        <v>319478.94622352632</v>
+        <v>319233.69800488785</v>
       </c>
       <c r="AA26" s="8">
-        <v>340551.05860484333</v>
+        <v>339929.95464690134</v>
       </c>
     </row>
     <row r="27" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -25068,10 +25068,10 @@
         <v>259849.49658743993</v>
       </c>
       <c r="Z27" s="8">
-        <v>278935.97547739197</v>
+        <v>278935.97547739348</v>
       </c>
       <c r="AA27" s="8">
-        <v>314734.50607646571</v>
+        <v>314414.09617819311</v>
       </c>
     </row>
     <row r="28" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -25317,10 +25317,10 @@
         <v>273996.09334580658</v>
       </c>
       <c r="Z30" s="8">
-        <v>254091.57027241727</v>
+        <v>253964.68704605958</v>
       </c>
       <c r="AA30" s="8">
-        <v>267301.73270928528</v>
+        <v>268008.19857064832</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -25486,10 +25486,10 @@
         <v>2285564.0565247671</v>
       </c>
       <c r="Z33" s="10">
-        <v>2401998.5929831276</v>
+        <v>2403539.1151501127</v>
       </c>
       <c r="AA33" s="10">
-        <v>2407377.1641075336</v>
+        <v>2406532.3248881213</v>
       </c>
     </row>
     <row r="34" spans="1:27" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -25544,7 +25544,7 @@
     </row>
     <row r="40" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -25555,7 +25555,7 @@
     </row>
     <row r="43" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -25761,7 +25761,7 @@
         <v>365531.34336379194</v>
       </c>
       <c r="AA49" s="8">
-        <v>378177.82972461358</v>
+        <v>377656.1037830459</v>
       </c>
     </row>
     <row r="50" spans="1:27" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -25841,10 +25841,10 @@
         <v>107178.80339277041</v>
       </c>
       <c r="Z50" s="8">
-        <v>104192.48991100464</v>
+        <v>104192.49087615307</v>
       </c>
       <c r="AA50" s="8">
-        <v>107768.11048849518</v>
+        <v>107662.36145199469</v>
       </c>
     </row>
     <row r="51" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -26007,7 +26007,7 @@
         <v>25695.602579257044</v>
       </c>
       <c r="Z52" s="8">
-        <v>23309.915510621235</v>
+        <v>23275.371476506345</v>
       </c>
       <c r="AA52" s="8">
         <v>36394.115900953584</v>
@@ -26422,10 +26422,10 @@
         <v>19686.129970004113</v>
       </c>
       <c r="Z57" s="8">
-        <v>18291.428066251268</v>
+        <v>18500.033952429305</v>
       </c>
       <c r="AA57" s="8">
-        <v>17945.592632405274</v>
+        <v>18151.836308365018</v>
       </c>
     </row>
     <row r="58" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -26588,7 +26588,7 @@
         <v>2111.394595788317</v>
       </c>
       <c r="Z59" s="8">
-        <v>2136.4998151467057</v>
+        <v>2130.4276199259289</v>
       </c>
       <c r="AA59" s="8">
         <v>2369.1217335378669</v>
@@ -26671,7 +26671,7 @@
         <v>1748.5288105788777</v>
       </c>
       <c r="Z60" s="8">
-        <v>1691.347251552472</v>
+        <v>1691.457635734381</v>
       </c>
       <c r="AA60" s="8">
         <v>1457.497379462146</v>
@@ -26837,10 +26837,10 @@
         <v>91602.265725282254</v>
       </c>
       <c r="Z62" s="8">
-        <v>90260.184938752791</v>
+        <v>90206.449262249487</v>
       </c>
       <c r="AA62" s="8">
-        <v>91228.152720935483</v>
+        <v>91026.823864296952</v>
       </c>
     </row>
     <row r="63" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -26920,10 +26920,10 @@
         <v>188533.07679822066</v>
       </c>
       <c r="Z63" s="8">
-        <v>180975.45381511346</v>
+        <v>180951.55778310419</v>
       </c>
       <c r="AA63" s="8">
-        <v>177370.00050749889</v>
+        <v>177363.1090225245</v>
       </c>
     </row>
     <row r="64" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -27006,7 +27006,7 @@
         <v>206805.96827842956</v>
       </c>
       <c r="AA64" s="8">
-        <v>225609.80903958704</v>
+        <v>225588.14445946849</v>
       </c>
     </row>
     <row r="65" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -27252,10 +27252,10 @@
         <v>203520.89047987183</v>
       </c>
       <c r="Z67" s="8">
-        <v>201977.55394357679</v>
+        <v>201651.71645276295</v>
       </c>
       <c r="AA67" s="8">
-        <v>202139.12378497852</v>
+        <v>202567.83079775705</v>
       </c>
     </row>
     <row r="68" spans="1:27" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -27421,10 +27421,10 @@
         <v>1805216.771038763</v>
       </c>
       <c r="Z70" s="10">
-        <v>1778234.5329187952</v>
+        <v>1777999.1647256417</v>
       </c>
       <c r="AA70" s="10">
-        <v>1833110.7044894486</v>
+        <v>1832888.2952783871</v>
       </c>
     </row>
     <row r="71" spans="1:27" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -27479,7 +27479,7 @@
     </row>
     <row r="77" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -27490,7 +27490,7 @@
     </row>
     <row r="80" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -27607,7 +27607,7 @@
         <v>64</v>
       </c>
       <c r="Z84" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA84" s="5"/>
     </row>
@@ -27688,10 +27688,10 @@
         <v>16.289362710970678</v>
       </c>
       <c r="Y86" s="14">
-        <v>9.5131892021121729</v>
+        <v>9.4040028630913071</v>
       </c>
       <c r="Z86" s="14">
-        <v>-20.515556850694765</v>
+        <v>-20.564052862609856</v>
       </c>
       <c r="AA86" s="14"/>
     </row>
@@ -27769,10 +27769,10 @@
         <v>12.257638378308556</v>
       </c>
       <c r="Y87" s="14">
-        <v>-18.228899227564668</v>
+        <v>-18.228898546547839</v>
       </c>
       <c r="Z87" s="14">
-        <v>-0.12202899143757406</v>
+        <v>-0.23647369269326646</v>
       </c>
       <c r="AA87" s="14"/>
     </row>
@@ -27931,10 +27931,10 @@
         <v>10.286717081469135</v>
       </c>
       <c r="Y89" s="14">
-        <v>-16.830616997407645</v>
+        <v>-16.751009942056655</v>
       </c>
       <c r="Z89" s="14">
-        <v>13.399576763678752</v>
+        <v>13.291138134238082</v>
       </c>
       <c r="AA89" s="14"/>
     </row>
@@ -28012,10 +28012,10 @@
         <v>8.4781078445053737</v>
       </c>
       <c r="Y90" s="14">
-        <v>5.9780305678433905</v>
+        <v>7.2999989197976873</v>
       </c>
       <c r="Z90" s="14">
-        <v>-15.636807831596158</v>
+        <v>-16.681458545720744</v>
       </c>
       <c r="AA90" s="14"/>
     </row>
@@ -28093,10 +28093,10 @@
         <v>17.740582691058265</v>
       </c>
       <c r="Y91" s="14">
-        <v>-17.902350227782748</v>
+        <v>-17.795809070868302</v>
       </c>
       <c r="Z91" s="14">
-        <v>20.537699610557908</v>
+        <v>20.381476116072264</v>
       </c>
       <c r="AA91" s="14"/>
     </row>
@@ -28255,10 +28255,10 @@
         <v>13.641746371183245</v>
       </c>
       <c r="Y93" s="14">
-        <v>60.484505950387614</v>
+        <v>58.32121316431315</v>
       </c>
       <c r="Z93" s="14">
-        <v>79.910084633617345</v>
+        <v>82.368366631659001</v>
       </c>
       <c r="AA93" s="14"/>
     </row>
@@ -28336,10 +28336,10 @@
         <v>17.206049223339576</v>
       </c>
       <c r="Y94" s="14">
-        <v>17.51780796948006</v>
+        <v>19.65392386757911</v>
       </c>
       <c r="Z94" s="14">
-        <v>-5.6070870448588579</v>
+        <v>-5.8761409625919754</v>
       </c>
       <c r="AA94" s="14"/>
     </row>
@@ -28420,7 +28420,7 @@
         <v>38.513624537738565</v>
       </c>
       <c r="Z95" s="14">
-        <v>15.497303044074158</v>
+        <v>15.488924128235013</v>
       </c>
       <c r="AA95" s="14"/>
     </row>
@@ -28498,10 +28498,10 @@
         <v>24.356776849360102</v>
       </c>
       <c r="Y96" s="14">
-        <v>53.130655577309597</v>
+        <v>52.51472655489178</v>
       </c>
       <c r="Z96" s="14">
-        <v>60.430415177874778</v>
+        <v>61.078311620524403</v>
       </c>
       <c r="AA96" s="14"/>
     </row>
@@ -28579,10 +28579,10 @@
         <v>-8.7052610673554085</v>
       </c>
       <c r="Y97" s="14">
-        <v>5.9376274710614609</v>
+        <v>5.9429052994272951</v>
       </c>
       <c r="Z97" s="14">
-        <v>-10.358820189565705</v>
+        <v>-10.363285904001344</v>
       </c>
       <c r="AA97" s="14"/>
     </row>
@@ -28660,10 +28660,10 @@
         <v>92.50491726216228</v>
       </c>
       <c r="Y98" s="14">
-        <v>-19.407407820807805</v>
+        <v>-18.982203834402128</v>
       </c>
       <c r="Z98" s="14">
-        <v>-12.131581528052848</v>
+        <v>-12.147187888357706</v>
       </c>
       <c r="AA98" s="14"/>
     </row>
@@ -28741,10 +28741,10 @@
         <v>17.343538725486283</v>
       </c>
       <c r="Y99" s="14">
-        <v>5.7889872781674541</v>
+        <v>5.6606067498338177</v>
       </c>
       <c r="Z99" s="14">
-        <v>3.4004762422068353</v>
+        <v>3.2283330839857598</v>
       </c>
       <c r="AA99" s="14"/>
     </row>
@@ -28822,10 +28822,10 @@
         <v>1.7329102746134168</v>
       </c>
       <c r="Y100" s="14">
-        <v>4.7920377630561717</v>
+        <v>4.7115940878385203</v>
       </c>
       <c r="Z100" s="14">
-        <v>6.5957749737203955</v>
+        <v>6.4831052521581114</v>
       </c>
       <c r="AA100" s="14"/>
     </row>
@@ -28903,10 +28903,10 @@
         <v>9.8287038747887294</v>
       </c>
       <c r="Y101" s="14">
-        <v>7.3452052594334702</v>
+        <v>7.3452052594340529</v>
       </c>
       <c r="Z101" s="14">
-        <v>12.833959670424534</v>
+        <v>12.719091053091859</v>
       </c>
       <c r="AA101" s="14"/>
     </row>
@@ -29146,10 +29146,10 @@
         <v>1.5540356531463146</v>
       </c>
       <c r="Y104" s="14">
-        <v>-7.26452805597782</v>
+        <v>-7.3108364630825804</v>
       </c>
       <c r="Z104" s="14">
-        <v>5.1989770548881609</v>
+        <v>5.5297103262398792</v>
       </c>
       <c r="AA104" s="14"/>
     </row>
@@ -29311,10 +29311,10 @@
         <v>8.6248310999405646</v>
       </c>
       <c r="Y107" s="14">
-        <v>5.0943457973083923</v>
+        <v>5.1617480721467359</v>
       </c>
       <c r="Z107" s="14">
-        <v>0.22392066090787921</v>
+        <v>0.12453343151945262</v>
       </c>
       <c r="AA107" s="14"/>
     </row>
@@ -29370,7 +29370,7 @@
     </row>
     <row r="114" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="115" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -29381,7 +29381,7 @@
     </row>
     <row r="117" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="118" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -29498,7 +29498,7 @@
         <v>64</v>
       </c>
       <c r="Z121" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA121" s="5"/>
     </row>
@@ -29582,7 +29582,7 @@
         <v>-4.8186440124165415</v>
       </c>
       <c r="Z123" s="14">
-        <v>3.4597542975228066</v>
+        <v>3.3170234617026892</v>
       </c>
       <c r="AA123" s="14"/>
     </row>
@@ -29660,10 +29660,10 @@
         <v>1.8348299805353889</v>
       </c>
       <c r="Y124" s="14">
-        <v>-2.7862911202899454</v>
+        <v>-2.7862902197868635</v>
       </c>
       <c r="Z124" s="14">
-        <v>3.4317450140068928</v>
+        <v>3.3302501424656583</v>
       </c>
       <c r="AA124" s="14"/>
     </row>
@@ -29822,10 +29822,10 @@
         <v>-6.6803643079937558</v>
       </c>
       <c r="Y126" s="14">
-        <v>-9.2844176791622317</v>
+        <v>-9.4188532659843105</v>
       </c>
       <c r="Z126" s="14">
-        <v>56.131479259847566</v>
+        <v>56.363201067226839</v>
       </c>
       <c r="AA126" s="14"/>
     </row>
@@ -30227,10 +30227,10 @@
         <v>-9.4708626718372102E-2</v>
       </c>
       <c r="Y131" s="14">
-        <v>-7.0846931615201214</v>
+        <v>-6.0250339674789899</v>
       </c>
       <c r="Z131" s="14">
-        <v>-1.8906967383486091</v>
+        <v>-1.8821459731351666</v>
       </c>
       <c r="AA131" s="14"/>
     </row>
@@ -30389,10 +30389,10 @@
         <v>3.4148496170849398</v>
       </c>
       <c r="Y133" s="14">
-        <v>1.1890349349414464</v>
+        <v>0.90144325345806919</v>
       </c>
       <c r="Z133" s="14">
-        <v>10.887991505638766</v>
+        <v>11.204047083291059</v>
       </c>
       <c r="AA133" s="14"/>
     </row>
@@ -30470,10 +30470,10 @@
         <v>0.75248594565474036</v>
       </c>
       <c r="Y134" s="14">
-        <v>-3.2702669055521483</v>
+        <v>-3.2639539308249965</v>
       </c>
       <c r="Z134" s="14">
-        <v>-13.826248387235523</v>
+        <v>-13.831872068770807</v>
       </c>
       <c r="AA134" s="14"/>
     </row>
@@ -30632,10 +30632,10 @@
         <v>-0.80789597342258901</v>
       </c>
       <c r="Y136" s="14">
-        <v>-1.4651174574157295</v>
+        <v>-1.523779408709018</v>
       </c>
       <c r="Z136" s="14">
-        <v>1.0724194536489335</v>
+        <v>0.90944118603144375</v>
       </c>
       <c r="AA136" s="14"/>
     </row>
@@ -30713,10 +30713,10 @@
         <v>2.9856342089165508</v>
       </c>
       <c r="Y137" s="14">
-        <v>-4.0086456506493136</v>
+        <v>-4.0213203666275774</v>
       </c>
       <c r="Z137" s="14">
-        <v>-1.9922333286689451</v>
+        <v>-1.9830991258339594</v>
       </c>
       <c r="AA137" s="14"/>
     </row>
@@ -30797,7 +30797,7 @@
         <v>6.487927943901667</v>
       </c>
       <c r="Z138" s="14">
-        <v>9.0925039145104591</v>
+        <v>9.0820281142717647</v>
       </c>
       <c r="AA138" s="14"/>
     </row>
@@ -31037,10 +31037,10 @@
         <v>-5.5827343938583738</v>
       </c>
       <c r="Y141" s="14">
-        <v>-0.75831848644926936</v>
+        <v>-0.91841875431147457</v>
       </c>
       <c r="Z141" s="14">
-        <v>7.9993958856874769E-2</v>
+        <v>0.45430525517431875</v>
       </c>
       <c r="AA141" s="14"/>
     </row>
@@ -31202,10 +31202,10 @@
         <v>1.2043335890745936</v>
       </c>
       <c r="Y144" s="14">
-        <v>-1.4946813342777432</v>
+        <v>-1.5077195575498479</v>
       </c>
       <c r="Z144" s="14">
-        <v>3.0859917831299555</v>
+        <v>3.0871291529102081</v>
       </c>
       <c r="AA144" s="14"/>
     </row>
@@ -31256,7 +31256,7 @@
     </row>
     <row r="150" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="151" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -31267,7 +31267,7 @@
     </row>
     <row r="153" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="154" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -31470,10 +31470,10 @@
         <v>108.15747324534905</v>
       </c>
       <c r="Z159" s="14">
-        <v>124.44317175608899</v>
+        <v>124.31909999414701</v>
       </c>
       <c r="AA159" s="14">
-        <v>95.605255182815725</v>
+        <v>95.583526551784331</v>
       </c>
     </row>
     <row r="160" spans="1:27" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -31553,10 +31553,10 @@
         <v>132.69324423591061</v>
       </c>
       <c r="Z160" s="14">
-        <v>111.61463512992944</v>
+        <v>111.61463502559241</v>
       </c>
       <c r="AA160" s="14">
-        <v>107.77970815564126</v>
+        <v>107.76195317734884</v>
       </c>
     </row>
     <row r="161" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -31719,7 +31719,7 @@
         <v>162.49479589015601</v>
       </c>
       <c r="Z162" s="14">
-        <v>148.97762401523045</v>
+        <v>149.34153668036058</v>
       </c>
       <c r="AA162" s="14">
         <v>108.20367289590035</v>
@@ -31802,10 +31802,10 @@
         <v>112.07943750890135</v>
       </c>
       <c r="Z163" s="14">
-        <v>123.23429929676242</v>
+        <v>124.77152208409564</v>
       </c>
       <c r="AA163" s="14">
-        <v>104.23416943973307</v>
+        <v>104.22757599211505</v>
       </c>
     </row>
     <row r="164" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -31885,7 +31885,7 @@
         <v>121.5407512219374</v>
       </c>
       <c r="Z164" s="14">
-        <v>101.79742047560258</v>
+        <v>101.92952675365645</v>
       </c>
       <c r="AA164" s="14">
         <v>130.03223704155599</v>
@@ -32051,7 +32051,7 @@
         <v>124.07624387842746</v>
       </c>
       <c r="Z166" s="14">
-        <v>183.79396762039295</v>
+        <v>181.31646886172706</v>
       </c>
       <c r="AA166" s="14">
         <v>298.73806214229609</v>
@@ -32134,10 +32134,10 @@
         <v>145.84660654323997</v>
       </c>
       <c r="Z167" s="14">
-        <v>184.46447720980476</v>
+        <v>185.69965483818805</v>
       </c>
       <c r="AA167" s="14">
-        <v>177.47694420113888</v>
+        <v>178.1405464748467</v>
       </c>
     </row>
     <row r="168" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -32220,7 +32220,7 @@
         <v>146.3919647904583</v>
       </c>
       <c r="AA168" s="14">
-        <v>157.79004822591932</v>
+        <v>157.77860112283128</v>
       </c>
     </row>
     <row r="169" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -32300,7 +32300,7 @@
         <v>101.07372281482945</v>
       </c>
       <c r="Z169" s="14">
-        <v>152.95615227702501</v>
+        <v>152.7751308597891</v>
       </c>
       <c r="AA169" s="14">
         <v>221.29374588379608</v>
@@ -32383,7 +32383,7 @@
         <v>88.19320548112195</v>
       </c>
       <c r="Z170" s="14">
-        <v>96.588490930862974</v>
+        <v>96.586999324512689</v>
       </c>
       <c r="AA170" s="14">
         <v>100.47498363607836</v>
@@ -32466,10 +32466,10 @@
         <v>131.66870065248952</v>
       </c>
       <c r="Z171" s="14">
-        <v>92.632722846637037</v>
+        <v>93.121450184484971</v>
       </c>
       <c r="AA171" s="14">
-        <v>69.737327369005015</v>
+        <v>70.092807883637647</v>
       </c>
     </row>
     <row r="172" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -32549,10 +32549,10 @@
         <v>132.73392225926952</v>
       </c>
       <c r="Z172" s="14">
-        <v>142.50574873521194</v>
+        <v>142.41759764935586</v>
       </c>
       <c r="AA172" s="14">
-        <v>145.78816225162805</v>
+        <v>145.69034407856631</v>
       </c>
     </row>
     <row r="173" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -32632,10 +32632,10 @@
         <v>161.70609981794598</v>
       </c>
       <c r="Z173" s="14">
-        <v>176.53164530804798</v>
+        <v>176.41942513008601</v>
       </c>
       <c r="AA173" s="14">
-        <v>192.00037076757263</v>
+        <v>191.65764319328176</v>
       </c>
     </row>
     <row r="174" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -32715,10 +32715,10 @@
         <v>133.80094732860076</v>
       </c>
       <c r="Z174" s="14">
-        <v>134.87810714526935</v>
+        <v>134.87810714527009</v>
       </c>
       <c r="AA174" s="14">
-        <v>139.50391049763277</v>
+        <v>139.37527476524104</v>
       </c>
     </row>
     <row r="175" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -32964,10 +32964,10 @@
         <v>134.62799455120543</v>
       </c>
       <c r="Z177" s="14">
-        <v>125.80188506659444</v>
+        <v>125.94223918027051</v>
       </c>
       <c r="AA177" s="14">
-        <v>132.23651498243467</v>
+        <v>132.30540975591859</v>
       </c>
     </row>
     <row r="178" spans="1:27" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -33133,10 +33133,10 @@
         <v>126.60884239456745</v>
       </c>
       <c r="Z180" s="14">
-        <v>135.07771604460328</v>
+        <v>135.18224096134469</v>
       </c>
       <c r="AA180" s="14">
-        <v>131.32742928245719</v>
+        <v>131.29727169339617</v>
       </c>
     </row>
     <row r="181" spans="1:27" s="1" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -33185,7 +33185,7 @@
     </row>
     <row r="187" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="188" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -33196,7 +33196,7 @@
     </row>
     <row r="190" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="191" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -33399,10 +33399,10 @@
         <v>18.173386798726774</v>
       </c>
       <c r="Z196" s="14">
-        <v>18.937513068215946</v>
+        <v>18.906506384773365</v>
       </c>
       <c r="AA196" s="14">
-        <v>15.018746731656748</v>
+        <v>14.999882548873867</v>
       </c>
     </row>
     <row r="197" spans="1:27" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -33482,10 +33482,10 @@
         <v>6.2224915967282657</v>
       </c>
       <c r="Z197" s="14">
-        <v>4.8415543533906336</v>
+        <v>4.8384512522580181</v>
       </c>
       <c r="AA197" s="14">
-        <v>4.8248424343764684</v>
+        <v>4.8210058239263525</v>
       </c>
     </row>
     <row r="198" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -33565,10 +33565,10 @@
         <v>3.9819682783631261</v>
       </c>
       <c r="Z198" s="14">
-        <v>5.2234820198772329</v>
+        <v>5.2201340860783825</v>
       </c>
       <c r="AA198" s="14">
-        <v>5.7386198084464075</v>
+        <v>5.7406344130412981</v>
       </c>
     </row>
     <row r="199" spans="1:27" s="10" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -33648,10 +33648,10 @@
         <v>1.8268583129276619</v>
       </c>
       <c r="Z199" s="14">
-        <v>1.4457359962294165</v>
+        <v>1.4461922925230193</v>
       </c>
       <c r="AA199" s="14">
-        <v>1.6357956164887693</v>
+        <v>1.6363698802447388</v>
       </c>
     </row>
     <row r="200" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -33731,10 +33731,10 @@
         <v>6.5839184176129439</v>
       </c>
       <c r="Z200" s="14">
-        <v>6.6392792307180617</v>
+        <v>6.7177890444844888</v>
       </c>
       <c r="AA200" s="14">
-        <v>5.588593879656818</v>
+        <v>5.5902021792371599</v>
       </c>
     </row>
     <row r="201" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -33814,10 +33814,10 @@
         <v>1.936138878593318</v>
       </c>
       <c r="Z201" s="14">
-        <v>1.5124738667834086</v>
+        <v>1.5134659984161585</v>
       </c>
       <c r="AA201" s="14">
-        <v>1.8190280266521954</v>
+        <v>1.819666616128943</v>
       </c>
     </row>
     <row r="202" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -33897,10 +33897,10 @@
         <v>1.5148566747540477</v>
       </c>
       <c r="Z202" s="14">
-        <v>2.1147496927043838</v>
+        <v>2.1133942669662709</v>
       </c>
       <c r="AA202" s="14">
-        <v>1.9118165701516525</v>
+        <v>1.912487734050879</v>
       </c>
     </row>
     <row r="203" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -33980,10 +33980,10 @@
         <v>0.32194199168523541</v>
       </c>
       <c r="Z203" s="14">
-        <v>0.49162208573938387</v>
+        <v>0.4846842851753787</v>
       </c>
       <c r="AA203" s="14">
-        <v>0.88250160710013903</v>
+        <v>0.88281141884094216</v>
       </c>
     </row>
     <row r="204" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34063,10 +34063,10 @@
         <v>1.2562129877295616</v>
       </c>
       <c r="Z204" s="14">
-        <v>1.4047130275256956</v>
+        <v>1.4293297320631793</v>
       </c>
       <c r="AA204" s="14">
-        <v>1.3229871038751344</v>
+        <v>1.3436669875790825</v>
       </c>
     </row>
     <row r="205" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34146,10 +34146,10 @@
         <v>0.39519355137933065</v>
       </c>
       <c r="Z205" s="14">
-        <v>0.52086238113196437</v>
+        <v>0.52052854007274263</v>
       </c>
       <c r="AA205" s="14">
-        <v>0.60023794600285574</v>
+        <v>0.60040510562936089</v>
       </c>
     </row>
     <row r="206" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34229,10 +34229,10 @@
         <v>9.3371485921915007E-2</v>
       </c>
       <c r="Z206" s="14">
-        <v>0.13604953475828735</v>
+        <v>0.13541546146261293</v>
       </c>
       <c r="AA206" s="14">
-        <v>0.21777718534755061</v>
+        <v>0.21785363838554725</v>
       </c>
     </row>
     <row r="207" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34312,10 +34312,10 @@
         <v>6.7470592320882372E-2</v>
       </c>
       <c r="Z207" s="14">
-        <v>6.8011979334520578E-2</v>
+        <v>6.7971773993748832E-2</v>
       </c>
       <c r="AA207" s="14">
-        <v>6.0830528566293597E-2</v>
+        <v>6.0851883781737372E-2</v>
       </c>
     </row>
     <row r="208" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34395,10 +34395,10 @@
         <v>0.11853147371308347</v>
       </c>
       <c r="Z208" s="14">
-        <v>9.0896980697527094E-2</v>
+        <v>9.1317983511516237E-2</v>
       </c>
       <c r="AA208" s="14">
-        <v>7.9691294105221661E-2</v>
+        <v>8.0125633277865232E-2</v>
       </c>
     </row>
     <row r="209" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34478,10 +34478,10 @@
         <v>5.3197931525227453</v>
       </c>
       <c r="Z209" s="14">
-        <v>5.3549553581133242</v>
+        <v>5.3450288016659648</v>
       </c>
       <c r="AA209" s="14">
-        <v>5.5246784463566323</v>
+        <v>5.5107214443026473</v>
       </c>
     </row>
     <row r="210" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34561,10 +34561,10 @@
         <v>13.338916688282797</v>
       </c>
       <c r="Z210" s="14">
-        <v>13.300546767879412</v>
+        <v>13.281818298386632</v>
       </c>
       <c r="AA210" s="14">
-        <v>14.146144762118857</v>
+        <v>14.125301834983853</v>
       </c>
     </row>
     <row r="211" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34644,10 +34644,10 @@
         <v>11.369162716994458</v>
       </c>
       <c r="Z211" s="14">
-        <v>11.612661901311585</v>
+        <v>11.605218892390381</v>
       </c>
       <c r="AA211" s="14">
-        <v>13.073751415812925</v>
+        <v>13.065026923866899</v>
       </c>
     </row>
     <row r="212" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34727,10 +34727,10 @@
         <v>3.4183243620608974</v>
       </c>
       <c r="Z212" s="14">
-        <v>3.4673716706590474</v>
+        <v>3.4651492966247921</v>
       </c>
       <c r="AA212" s="14">
-        <v>3.8209960295066514</v>
+        <v>3.8223374315188172</v>
       </c>
     </row>
     <row r="213" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34810,10 +34810,10 @@
         <v>3.8812966512643279E-2</v>
       </c>
       <c r="Z213" s="14">
-        <v>4.4337861969423235E-2</v>
+        <v>4.4309444100635462E-2</v>
       </c>
       <c r="AA213" s="14">
-        <v>4.3963083693591608E-2</v>
+        <v>4.3978517409950423E-2</v>
       </c>
     </row>
     <row r="214" spans="1:27" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34893,10 +34893,10 @@
         <v>11.988117006111024</v>
       </c>
       <c r="Z214" s="14">
-        <v>10.578339679910133</v>
+        <v>10.566280592034312</v>
       </c>
       <c r="AA214" s="14">
-        <v>11.10344223142865</v>
+        <v>11.136696390858075</v>
       </c>
     </row>
     <row r="215" spans="1:27" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -34976,10 +34976,10 @@
         <v>12.034532067059294</v>
       </c>
       <c r="Z215" s="14">
-        <v>12.214842543050617</v>
+        <v>12.207013573018388</v>
       </c>
       <c r="AA215" s="14">
-        <v>12.58555529865642</v>
+        <v>12.589973594061982</v>
       </c>
     </row>
     <row r="216" spans="1:27" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -35120,7 +35120,7 @@
     </row>
     <row r="224" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="225" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -35131,7 +35131,7 @@
     </row>
     <row r="227" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="228" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -35334,10 +35334,10 @@
         <v>21.273716886451524</v>
       </c>
       <c r="Z233" s="14">
-        <v>20.555856755509556</v>
+        <v>20.558577901255433</v>
       </c>
       <c r="AA233" s="14">
-        <v>20.630386849982543</v>
+        <v>20.604425526416808</v>
       </c>
     </row>
     <row r="234" spans="1:27" s="10" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -35417,10 +35417,10 @@
         <v>5.9371708213799321</v>
       </c>
       <c r="Z234" s="14">
-        <v>5.8593221525162384</v>
+        <v>5.8600978528710801</v>
       </c>
       <c r="AA234" s="14">
-        <v>5.8789744789860015</v>
+        <v>5.8739183249376614</v>
       </c>
     </row>
     <row r="235" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -35500,10 +35500,10 @@
         <v>4.6919088845975061</v>
       </c>
       <c r="Z235" s="14">
-        <v>4.6316117514085162</v>
+        <v>4.6322248754813193</v>
       </c>
       <c r="AA235" s="14">
-        <v>4.4732117932911253</v>
+        <v>4.4737545887841286</v>
       </c>
     </row>
     <row r="236" spans="1:27" s="10" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -35583,10 +35583,10 @@
         <v>1.4234081464062183</v>
       </c>
       <c r="Z236" s="14">
-        <v>1.3108459586801706</v>
+        <v>1.3090766260341806</v>
       </c>
       <c r="AA236" s="14">
-        <v>1.9853746864180768</v>
+        <v>1.9856155988723736</v>
       </c>
     </row>
     <row r="237" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -35666,10 +35666,10 @@
         <v>7.4374239182637236</v>
       </c>
       <c r="Z237" s="14">
-        <v>7.2773463214824918</v>
+        <v>7.2783096829331733</v>
       </c>
       <c r="AA237" s="14">
-        <v>7.0412195104922528</v>
+        <v>7.0420739172121136</v>
       </c>
     </row>
     <row r="238" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -35749,10 +35749,10 @@
         <v>2.0168733504550778</v>
       </c>
       <c r="Z238" s="14">
-        <v>2.0069419691358146</v>
+        <v>2.0072076443478233</v>
       </c>
       <c r="AA238" s="14">
-        <v>1.8371465412582992</v>
+        <v>1.8373694671801339</v>
       </c>
     </row>
     <row r="239" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -35832,10 +35832,10 @@
         <v>1.6599765384894292</v>
       </c>
       <c r="Z239" s="14">
-        <v>1.665654725029907</v>
+        <v>1.6658752212769388</v>
       </c>
       <c r="AA239" s="14">
-        <v>1.5970970080268141</v>
+        <v>1.5972908054810608</v>
       </c>
     </row>
     <row r="240" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -35915,10 +35915,10 @@
         <v>0.32851335284945704</v>
       </c>
       <c r="Z240" s="14">
-        <v>0.36131321043091652</v>
+        <v>0.36136104039573813</v>
       </c>
       <c r="AA240" s="14">
-        <v>0.38795413803981216</v>
+        <v>0.3880012137803206</v>
       </c>
     </row>
     <row r="241" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -35998,10 +35998,10 @@
         <v>1.0905133547300396</v>
       </c>
       <c r="Z241" s="14">
-        <v>1.028628548576644</v>
+        <v>1.0404973365262518</v>
       </c>
       <c r="AA241" s="14">
-        <v>0.9789693873073213</v>
+        <v>0.99034056549572969</v>
       </c>
     </row>
     <row r="242" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36081,10 +36081,10 @@
         <v>0.49669509792413491</v>
       </c>
       <c r="Z242" s="14">
-        <v>0.4806063018388097</v>
+        <v>0.48066992359922789</v>
       </c>
       <c r="AA242" s="14">
-        <v>0.49957337165823112</v>
+        <v>0.49963399167514333</v>
       </c>
     </row>
     <row r="243" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36164,10 +36164,10 @@
         <v>0.11696072347994931</v>
       </c>
       <c r="Z243" s="14">
-        <v>0.12014724579889097</v>
+        <v>0.1198216322140213</v>
       </c>
       <c r="AA243" s="14">
-        <v>0.12924051601115419</v>
+        <v>0.12925619851688966</v>
       </c>
     </row>
     <row r="244" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36247,10 +36247,10 @@
         <v>9.6859769897480741E-2</v>
       </c>
       <c r="Z244" s="14">
-        <v>9.5113845797173538E-2</v>
+        <v>9.5132645126713836E-2</v>
       </c>
       <c r="AA244" s="14">
-        <v>7.9509512212907127E-2</v>
+        <v>7.9519160181050472E-2</v>
       </c>
     </row>
     <row r="245" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36330,10 +36330,10 @@
         <v>0.1139764621338796</v>
       </c>
       <c r="Z245" s="14">
-        <v>0.13254664410869249</v>
+        <v>0.13256419038472647</v>
       </c>
       <c r="AA245" s="14">
-        <v>0.15007246744133887</v>
+        <v>0.1500906777704526</v>
       </c>
     </row>
     <row r="246" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36413,10 +36413,10 @@
         <v>5.0743083708762695</v>
       </c>
       <c r="Z246" s="14">
-        <v>5.0758312960326819</v>
+        <v>5.0734809696138976</v>
       </c>
       <c r="AA246" s="14">
-        <v>4.9766853958961539</v>
+        <v>4.9663050442728371</v>
       </c>
     </row>
     <row r="247" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36496,10 +36496,10 @@
         <v>10.443791561372123</v>
       </c>
       <c r="Z247" s="14">
-        <v>10.177254488363818</v>
+        <v>10.177257749782259</v>
       </c>
       <c r="AA247" s="14">
-        <v>9.6759022831029373</v>
+        <v>9.6767004011876132</v>
       </c>
     </row>
     <row r="248" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36579,10 +36579,10 @@
         <v>10.758044388572543</v>
       </c>
       <c r="Z248" s="14">
-        <v>11.629847719748089</v>
+        <v>11.63138725716675</v>
       </c>
       <c r="AA248" s="14">
-        <v>12.307484129957283</v>
+        <v>12.307795572735936</v>
       </c>
     </row>
     <row r="249" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36662,10 +36662,10 @@
         <v>4.1262348858801028</v>
       </c>
       <c r="Z249" s="14">
-        <v>4.2367334584348031</v>
+        <v>4.2372943092601405</v>
       </c>
       <c r="AA249" s="14">
-        <v>4.2602833833163896</v>
+        <v>4.2608003413157522</v>
       </c>
     </row>
     <row r="250" spans="1:27" s="10" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36745,10 +36745,10 @@
         <v>0.12300485927010481</v>
       </c>
       <c r="Z250" s="14">
-        <v>0.15643142249134631</v>
+        <v>0.1564521305895247</v>
       </c>
       <c r="AA250" s="14">
-        <v>0.1510292107990768</v>
+        <v>0.15104753722284611</v>
       </c>
     </row>
     <row r="251" spans="1:27" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36828,10 +36828,10 @@
         <v>11.274041641146578</v>
       </c>
       <c r="Z251" s="14">
-        <v>11.358319175820453</v>
+        <v>11.341496692090926</v>
       </c>
       <c r="AA251" s="14">
-        <v>11.027109453341913</v>
+        <v>11.05183721886282</v>
       </c>
     </row>
     <row r="252" spans="1:27" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -36911,10 +36911,10 @@
         <v>11.516576985823937</v>
       </c>
       <c r="Z252" s="14">
-        <v>11.839647008795007</v>
+        <v>11.841214319049884</v>
       </c>
       <c r="AA252" s="14">
-        <v>11.932775882460355</v>
+        <v>11.934223848098318</v>
       </c>
     </row>
     <row r="253" spans="1:27" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
